--- a/KGEN/registry/CoinMarketCap/KGEN_CMC_EMISSION_RELEASE_SCHEDULE_V1.xlsx
+++ b/KGEN/registry/CoinMarketCap/KGEN_CMC_EMISSION_RELEASE_SCHEDULE_V1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emission Schedule" sheetId="1" r:id="Ref1e48876c4b4f15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Summary" sheetId="2" r:id="R022b63ca617c447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emission Schedule" sheetId="1" r:id="Rc21e10ac79f44ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Summary" sheetId="2" r:id="Rea348a8e64a641a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -560,8 +560,7 @@
         <x:v>71980505.786117825703641</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:f>"2896511.372639273602111511"</x:f>
-        <x:v>2896511.372639273602111511</x:v>
+        <x:v>4366878.985936300061217422</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
         <x:f>"0"</x:f>
@@ -572,7 +571,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="20" t="str">
-        <x:v>Supply decreased by verified burns and circulating supply excludes non-public balances</x:v>
+        <x:v>Supply decreased by verified burns and circulating supply excludes evidenced non-public balances</x:v>
       </x:c>
       <x:c r="J3" s="20" t="str">
         <x:v>https://klineodyssey.github.io/kline-odyssey/KGEN/registry/CoinMarketCap/KGEN_CMC_CIRCULATING_SUPPLY_VERIFICATION.md</x:v>
@@ -751,10 +750,10 @@
         <x:v>Current circulating supply</x:v>
       </x:c>
       <x:c r="B15" s="48" t="str">
-        <x:v>2896511.372639273602111511</x:v>
+        <x:v>4366878.985936300061217422</x:v>
       </x:c>
       <x:c r="C15" s="48" t="str">
-        <x:v>PR #55 methodology</x:v>
+        <x:v>Corrected frozen-block methodology</x:v>
       </x:c>
       <x:c r="D15" s="51" t="str">
         <x:v>VERIFIED</x:v>
